--- a/Fase 2/Evidencias Proyecto/Evidencias Documentación/Sprint 4/Extras/Sprint-backlog 4-Burndown Chart.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias Documentación/Sprint 4/Extras/Sprint-backlog 4-Burndown Chart.xlsx
@@ -1,15 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol.KLAXMVN\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5F63EE-614A-4BBA-ABDA-BA72610A97A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="VSzw61OUxzfnFMmdB4FHQfl60NlDJbS+HFZj7C2HwuI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="0nC9AceKedwtKpRHCzXtvyWgQa7ET/ZvhLEoLewf+ZI="/>
     </ext>
   </extLst>
 </workbook>
@@ -81,16 +101,22 @@
     <t>Revisión del Sprint</t>
   </si>
   <si>
-    <t>HU #7 Event Forecast Scen</t>
+    <t>Yojan</t>
   </si>
   <si>
-    <t>T4.1 Ajustar Prophet para aforo/eventos como parámetro adicional</t>
+    <t>Finalizado</t>
   </si>
   <si>
     <t>Sergio</t>
   </si>
   <si>
-    <t>Finalizado</t>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>HU #7 Event Forecast Scen</t>
+  </si>
+  <si>
+    <t>T4.1 Ajustar Prophet para aforo/eventos como parámetro adicional</t>
   </si>
   <si>
     <t>T4.2 Endpoint forecast con escenarios personalizados</t>
@@ -108,9 +134,6 @@
     <t>T4.8: Pantalla consulta de auditoría</t>
   </si>
   <si>
-    <t>Yojan</t>
-  </si>
-  <si>
     <t>HU #12 Audit Log</t>
   </si>
   <si>
@@ -122,34 +145,31 @@
   <si>
     <t>T4.9: Testing integral seguridad + cierre de MVP</t>
   </si>
-  <si>
-    <t>Total</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -159,7 +179,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -187,12 +207,19 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -207,95 +234,151 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="1400">
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="757575"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" i="0" sz="1400">
-                <a:solidFill>
-                  <a:srgbClr val="757575"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Gráfico de trabajo pendiente - Sprint 4</a:t>
+              <a:rPr lang="es-MX"/>
+              <a:t>Gráfico de trabajo pendiente</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="es-MX"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Sprint 4</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
+          <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.07493754028077451"/>
+          <c:x val="7.4937540280774512E-2"/>
           <c:y val="0.11953713440543061"/>
-          <c:w val="0.8809708110329625"/>
+          <c:w val="0.88097081103296249"/>
           <c:h val="0.7630747133806971"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -304,11 +387,13 @@
             <c:v>Sprint Burndown Chart</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln cmpd="sng" w="28575">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -317,46 +402,166 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln cmpd="sng">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:trendline>
-            <c:name>Linear (Sprint Burndown Chart)</c:name>
             <c:spPr>
-              <a:ln w="19050">
+              <a:ln w="9525" cap="rnd">
                 <a:solidFill>
-                  <a:srgbClr val="000000">
-                    <a:alpha val="0"/>
-                  </a:srgbClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
+                <a:prstDash val="solid"/>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
+            <c:intercept val="7"/>
             <c:dispRSqr val="0"/>
             <c:dispEq val="0"/>
           </c:trendline>
           <c:cat>
             <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$F$6:$T$6</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
               <c:f>Sheet1!$F$6:$S$6</c:f>
+              <c:strCache>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>Día 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Día 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Día 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Día 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Día 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Día 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Día 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Día 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Día 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Día 10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Día 11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Día 12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Día 13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Día 14</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$E$18:$T$18</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
               <c:f>Sheet1!$E$18:$R$18</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4468-4C98-A6BD-DC2791884EDE}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="487935565"/>
-        <c:axId val="334323424"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1895874766"/>
+        <c:axId val="87643822"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="487935565"/>
+        <c:axId val="1895874766"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -365,140 +570,818 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="es-MX"/>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:spPr/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="334323424"/>
+        <c:crossAx val="87643822"/>
+        <c:crossesAt val="0"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="334323424"/>
+        <c:axId val="87643822"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="7.0"/>
+          <c:max val="7"/>
+          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B7B7B7"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr lvl="0">
-                  <a:defRPr b="0">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:srgbClr val="000000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:r>
-                  <a:rPr b="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                  </a:rPr>
-                  <a:t/>
-                </a:r>
+                <a:endParaRPr lang="es-MX"/>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr lvl="0">
-              <a:defRPr b="0" i="0" sz="900">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487935565"/>
-        <c:majorUnit val="1.0"/>
-        <c:minorUnit val="1.0"/>
+        <c:crossAx val="1895874766"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="1"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:colOff>443345</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14316075" cy="4886325"/>
-    <xdr:graphicFrame>
+    <xdr:ext cx="14316941" cy="4888923"/>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="514075883" name="Chart 1" title="Gráfico"/>
+        <xdr:cNvPr id="514075883" name="Chart 1" title="Gráfico">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000EB2CA41E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -507,7 +1390,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -517,7 +1400,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -707,25 +1590,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ960"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="59.0"/>
-    <col customWidth="1" min="2" max="2" width="11.33"/>
-    <col customWidth="1" min="3" max="3" width="19.11"/>
-    <col customWidth="1" min="4" max="4" width="18.89"/>
-    <col customWidth="1" min="5" max="5" width="15.33"/>
-    <col customWidth="1" min="20" max="20" width="14.33"/>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="18.875" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="20" max="20" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -763,7 +1646,7 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="1"/>
@@ -801,7 +1684,7 @@
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:36" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -841,7 +1724,7 @@
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="1"/>
@@ -879,7 +1762,7 @@
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="1"/>
@@ -917,7 +1800,7 @@
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
     </row>
-    <row r="6" ht="30.75" customHeight="1">
+    <row r="6" spans="1:36" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
@@ -995,12 +1878,12 @@
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:36" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1037,64 +1920,64 @@
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" s="11">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F8" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S8" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T8" s="11">
-        <f t="shared" ref="T8:T9" si="1">SUM(F8:S8)</f>
+        <f t="shared" ref="T8:T17" si="0">SUM(F8:S8)</f>
         <v>6</v>
       </c>
       <c r="U8" s="1"/>
@@ -1114,64 +1997,64 @@
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" s="11">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H9" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I9" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S9" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="U9" s="1"/>
@@ -1191,12 +2074,12 @@
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:36" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -1233,64 +2116,64 @@
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E11" s="11">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F11" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H11" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S11" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T11" s="11">
-        <f t="shared" ref="T11:T13" si="2">SUM(F11:S11)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="U11" s="1"/>
@@ -1310,64 +2193,64 @@
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E12" s="11">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S12" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T12" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="U12" s="1"/>
@@ -1387,62 +2270,62 @@
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" s="11">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G13" s="11">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M13" s="11"/>
       <c r="N13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S13" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T13" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="U13" s="1"/>
@@ -1462,12 +2345,12 @@
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:36" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1504,64 +2387,64 @@
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="11">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J15" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S15" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T15" s="11">
-        <f t="shared" ref="T15:T17" si="3">SUM(F15:S15)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="U15" s="1"/>
@@ -1581,64 +2464,64 @@
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16" s="11">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L16" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N16" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S16" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T16" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="U16" s="1"/>
@@ -1658,64 +2541,64 @@
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E17" s="11">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M17" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="S17" s="11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="T17" s="11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="U17" s="1"/>
@@ -1735,75 +2618,75 @@
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
     </row>
-    <row r="18" ht="28.5" customHeight="1">
+    <row r="18" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12">
-        <f t="shared" ref="E18:T18" si="4">SUM(E7:E17)</f>
+        <f t="shared" ref="E18:T18" si="1">SUM(E7:E17)</f>
         <v>44</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="G18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="I18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="M18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="O18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="P18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="U18" s="1"/>
@@ -1823,7 +2706,7 @@
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -1861,7 +2744,7 @@
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="1"/>
@@ -1899,7 +2782,7 @@
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="1"/>
@@ -1937,7 +2820,7 @@
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="1"/>
@@ -1975,7 +2858,7 @@
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="1"/>
@@ -2013,7 +2896,7 @@
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="1"/>
@@ -2051,7 +2934,7 @@
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="1"/>
@@ -2089,7 +2972,7 @@
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="1"/>
@@ -2127,7 +3010,7 @@
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="1"/>
@@ -2165,7 +3048,7 @@
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="1"/>
@@ -2203,7 +3086,7 @@
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="1"/>
@@ -2241,7 +3124,7 @@
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
@@ -2279,7 +3162,7 @@
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -2317,7 +3200,7 @@
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="1"/>
@@ -2355,7 +3238,7 @@
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
       <c r="C33" s="1"/>
@@ -2393,7 +3276,7 @@
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
       <c r="C34" s="1"/>
@@ -2431,7 +3314,7 @@
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
       <c r="C35" s="1"/>
@@ -2469,7 +3352,7 @@
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
       <c r="C36" s="1"/>
@@ -2507,7 +3390,7 @@
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
       <c r="C37" s="1"/>
@@ -2545,7 +3428,7 @@
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
       <c r="C38" s="1"/>
@@ -2583,7 +3466,7 @@
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="C39" s="1"/>
@@ -2621,7 +3504,7 @@
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="1"/>
@@ -2659,7 +3542,7 @@
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
       <c r="C41" s="1"/>
@@ -2697,7 +3580,7 @@
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
       <c r="C42" s="1"/>
@@ -2735,7 +3618,7 @@
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="2"/>
       <c r="C43" s="1"/>
@@ -2773,7 +3656,7 @@
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="1"/>
@@ -2811,7 +3694,7 @@
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="1"/>
@@ -2849,7 +3732,7 @@
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="1"/>
@@ -2887,7 +3770,7 @@
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="1"/>
@@ -2925,7 +3808,7 @@
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="1"/>
@@ -2963,7 +3846,7 @@
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="1"/>
@@ -3001,7 +3884,7 @@
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="1"/>
@@ -3039,7 +3922,7 @@
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="1"/>
@@ -3077,7 +3960,7 @@
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="1"/>
@@ -3115,7 +3998,7 @@
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="1"/>
@@ -3153,7 +4036,7 @@
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="1"/>
@@ -3191,7 +4074,7 @@
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="1"/>
@@ -3229,7 +4112,7 @@
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="1"/>
@@ -3267,7 +4150,7 @@
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="1"/>
@@ -3305,7 +4188,7 @@
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="1"/>
@@ -3343,7 +4226,7 @@
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="1"/>
@@ -3381,7 +4264,7 @@
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="1"/>
@@ -3419,7 +4302,7 @@
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="1"/>
@@ -3457,7 +4340,7 @@
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="1"/>
@@ -3495,7 +4378,7 @@
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="1"/>
@@ -3533,7 +4416,7 @@
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="1"/>
@@ -3571,7 +4454,7 @@
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="1"/>
@@ -3609,7 +4492,7 @@
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="1"/>
@@ -3647,7 +4530,7 @@
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="1"/>
@@ -3685,7 +4568,7 @@
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="1"/>
@@ -3723,7 +4606,7 @@
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="1"/>
@@ -3761,7 +4644,7 @@
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="1"/>
@@ -3799,7 +4682,7 @@
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="1"/>
@@ -3837,7 +4720,7 @@
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="1"/>
@@ -3875,7 +4758,7 @@
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="1"/>
@@ -3913,7 +4796,7 @@
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="1"/>
@@ -3951,7 +4834,7 @@
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="1"/>
@@ -3989,7 +4872,7 @@
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="1"/>
@@ -4027,7 +4910,7 @@
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="1"/>
@@ -4065,7 +4948,7 @@
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="1"/>
@@ -4103,7 +4986,7 @@
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="1"/>
@@ -4141,7 +5024,7 @@
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="1"/>
@@ -4179,7 +5062,7 @@
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="1"/>
@@ -4217,7 +5100,7 @@
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="1"/>
@@ -4255,7 +5138,7 @@
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="1"/>
@@ -4293,7 +5176,7 @@
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="1"/>
@@ -4331,7 +5214,7 @@
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="1"/>
@@ -4369,7 +5252,7 @@
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="1"/>
@@ -4407,7 +5290,7 @@
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="1"/>
@@ -4445,7 +5328,7 @@
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="1"/>
@@ -4483,7 +5366,7 @@
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="1"/>
@@ -4521,7 +5404,7 @@
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="1"/>
@@ -4559,7 +5442,7 @@
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="1"/>
@@ -4597,7 +5480,7 @@
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="1"/>
@@ -4635,7 +5518,7 @@
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="1"/>
@@ -4673,7 +5556,7 @@
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="1"/>
@@ -4711,7 +5594,7 @@
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="1"/>
@@ -4749,7 +5632,7 @@
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="1"/>
@@ -4787,2601 +5670,2600 @@
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B97" s="13"/>
     </row>
-    <row r="98">
+    <row r="98" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B98" s="13"/>
     </row>
-    <row r="99">
+    <row r="99" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B99" s="13"/>
     </row>
-    <row r="100">
+    <row r="100" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B100" s="13"/>
     </row>
-    <row r="101">
+    <row r="101" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B101" s="13"/>
     </row>
-    <row r="102">
+    <row r="102" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B102" s="13"/>
     </row>
-    <row r="103">
+    <row r="103" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B103" s="13"/>
     </row>
-    <row r="104">
+    <row r="104" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B104" s="13"/>
     </row>
-    <row r="105">
+    <row r="105" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B105" s="13"/>
     </row>
-    <row r="106">
+    <row r="106" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B106" s="13"/>
     </row>
-    <row r="107">
+    <row r="107" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B107" s="13"/>
     </row>
-    <row r="108">
+    <row r="108" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B108" s="13"/>
     </row>
-    <row r="109">
+    <row r="109" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B109" s="13"/>
     </row>
-    <row r="110">
+    <row r="110" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B110" s="13"/>
     </row>
-    <row r="111">
+    <row r="111" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="13"/>
     </row>
-    <row r="112">
+    <row r="112" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B112" s="13"/>
     </row>
-    <row r="113">
+    <row r="113" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B113" s="13"/>
     </row>
-    <row r="114">
+    <row r="114" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B114" s="13"/>
     </row>
-    <row r="115">
+    <row r="115" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B115" s="13"/>
     </row>
-    <row r="116">
+    <row r="116" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B116" s="13"/>
     </row>
-    <row r="117">
+    <row r="117" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B117" s="13"/>
     </row>
-    <row r="118">
+    <row r="118" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B118" s="13"/>
     </row>
-    <row r="119">
+    <row r="119" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B119" s="13"/>
     </row>
-    <row r="120">
+    <row r="120" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B120" s="13"/>
     </row>
-    <row r="121">
+    <row r="121" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B121" s="13"/>
     </row>
-    <row r="122">
+    <row r="122" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B122" s="13"/>
     </row>
-    <row r="123">
+    <row r="123" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B123" s="13"/>
     </row>
-    <row r="124">
+    <row r="124" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B124" s="13"/>
     </row>
-    <row r="125">
+    <row r="125" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B125" s="13"/>
     </row>
-    <row r="126">
+    <row r="126" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B126" s="13"/>
     </row>
-    <row r="127">
+    <row r="127" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B127" s="13"/>
     </row>
-    <row r="128">
+    <row r="128" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B128" s="13"/>
     </row>
-    <row r="129">
+    <row r="129" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B129" s="13"/>
     </row>
-    <row r="130">
+    <row r="130" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B130" s="13"/>
     </row>
-    <row r="131">
+    <row r="131" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B131" s="13"/>
     </row>
-    <row r="132">
+    <row r="132" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B132" s="13"/>
     </row>
-    <row r="133">
+    <row r="133" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B133" s="13"/>
     </row>
-    <row r="134">
+    <row r="134" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B134" s="13"/>
     </row>
-    <row r="135">
+    <row r="135" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B135" s="13"/>
     </row>
-    <row r="136">
+    <row r="136" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B136" s="13"/>
     </row>
-    <row r="137">
+    <row r="137" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B137" s="13"/>
     </row>
-    <row r="138">
+    <row r="138" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B138" s="13"/>
     </row>
-    <row r="139">
+    <row r="139" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B139" s="13"/>
     </row>
-    <row r="140">
+    <row r="140" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B140" s="13"/>
     </row>
-    <row r="141">
+    <row r="141" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B141" s="13"/>
     </row>
-    <row r="142">
+    <row r="142" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B142" s="13"/>
     </row>
-    <row r="143">
+    <row r="143" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B143" s="13"/>
     </row>
-    <row r="144">
+    <row r="144" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B144" s="13"/>
     </row>
-    <row r="145">
+    <row r="145" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B145" s="13"/>
     </row>
-    <row r="146">
+    <row r="146" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B146" s="13"/>
     </row>
-    <row r="147">
+    <row r="147" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B147" s="13"/>
     </row>
-    <row r="148">
+    <row r="148" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B148" s="13"/>
     </row>
-    <row r="149">
+    <row r="149" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B149" s="13"/>
     </row>
-    <row r="150">
+    <row r="150" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B150" s="13"/>
     </row>
-    <row r="151">
+    <row r="151" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B151" s="13"/>
     </row>
-    <row r="152">
+    <row r="152" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B152" s="13"/>
     </row>
-    <row r="153">
+    <row r="153" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B153" s="13"/>
     </row>
-    <row r="154">
+    <row r="154" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B154" s="13"/>
     </row>
-    <row r="155">
+    <row r="155" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B155" s="13"/>
     </row>
-    <row r="156">
+    <row r="156" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B156" s="13"/>
     </row>
-    <row r="157">
+    <row r="157" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B157" s="13"/>
     </row>
-    <row r="158">
+    <row r="158" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B158" s="13"/>
     </row>
-    <row r="159">
+    <row r="159" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B159" s="13"/>
     </row>
-    <row r="160">
+    <row r="160" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B160" s="13"/>
     </row>
-    <row r="161">
+    <row r="161" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B161" s="13"/>
     </row>
-    <row r="162">
+    <row r="162" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B162" s="13"/>
     </row>
-    <row r="163">
+    <row r="163" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B163" s="13"/>
     </row>
-    <row r="164">
+    <row r="164" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B164" s="13"/>
     </row>
-    <row r="165">
+    <row r="165" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B165" s="13"/>
     </row>
-    <row r="166">
+    <row r="166" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B166" s="13"/>
     </row>
-    <row r="167">
+    <row r="167" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B167" s="13"/>
     </row>
-    <row r="168">
+    <row r="168" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B168" s="13"/>
     </row>
-    <row r="169">
+    <row r="169" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B169" s="13"/>
     </row>
-    <row r="170">
+    <row r="170" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B170" s="13"/>
     </row>
-    <row r="171">
+    <row r="171" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B171" s="13"/>
     </row>
-    <row r="172">
+    <row r="172" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B172" s="13"/>
     </row>
-    <row r="173">
+    <row r="173" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B173" s="13"/>
     </row>
-    <row r="174">
+    <row r="174" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B174" s="13"/>
     </row>
-    <row r="175">
+    <row r="175" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B175" s="13"/>
     </row>
-    <row r="176">
+    <row r="176" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B176" s="13"/>
     </row>
-    <row r="177">
+    <row r="177" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B177" s="13"/>
     </row>
-    <row r="178">
+    <row r="178" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B178" s="13"/>
     </row>
-    <row r="179">
+    <row r="179" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B179" s="13"/>
     </row>
-    <row r="180">
+    <row r="180" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B180" s="13"/>
     </row>
-    <row r="181">
+    <row r="181" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B181" s="13"/>
     </row>
-    <row r="182">
+    <row r="182" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B182" s="13"/>
     </row>
-    <row r="183">
+    <row r="183" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B183" s="13"/>
     </row>
-    <row r="184">
+    <row r="184" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B184" s="13"/>
     </row>
-    <row r="185">
+    <row r="185" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B185" s="13"/>
     </row>
-    <row r="186">
+    <row r="186" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B186" s="13"/>
     </row>
-    <row r="187">
+    <row r="187" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B187" s="13"/>
     </row>
-    <row r="188">
+    <row r="188" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B188" s="13"/>
     </row>
-    <row r="189">
+    <row r="189" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B189" s="13"/>
     </row>
-    <row r="190">
+    <row r="190" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B190" s="13"/>
     </row>
-    <row r="191">
+    <row r="191" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B191" s="13"/>
     </row>
-    <row r="192">
+    <row r="192" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B192" s="13"/>
     </row>
-    <row r="193">
+    <row r="193" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B193" s="13"/>
     </row>
-    <row r="194">
+    <row r="194" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B194" s="13"/>
     </row>
-    <row r="195">
+    <row r="195" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B195" s="13"/>
     </row>
-    <row r="196">
+    <row r="196" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B196" s="13"/>
     </row>
-    <row r="197">
+    <row r="197" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B197" s="13"/>
     </row>
-    <row r="198">
+    <row r="198" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B198" s="13"/>
     </row>
-    <row r="199">
+    <row r="199" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B199" s="13"/>
     </row>
-    <row r="200">
+    <row r="200" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B200" s="13"/>
     </row>
-    <row r="201">
+    <row r="201" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B201" s="13"/>
     </row>
-    <row r="202">
+    <row r="202" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B202" s="13"/>
     </row>
-    <row r="203">
+    <row r="203" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B203" s="13"/>
     </row>
-    <row r="204">
+    <row r="204" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B204" s="13"/>
     </row>
-    <row r="205">
+    <row r="205" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B205" s="13"/>
     </row>
-    <row r="206">
+    <row r="206" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B206" s="13"/>
     </row>
-    <row r="207">
+    <row r="207" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B207" s="13"/>
     </row>
-    <row r="208">
+    <row r="208" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B208" s="13"/>
     </row>
-    <row r="209">
+    <row r="209" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B209" s="13"/>
     </row>
-    <row r="210">
+    <row r="210" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B210" s="13"/>
     </row>
-    <row r="211">
+    <row r="211" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B211" s="13"/>
     </row>
-    <row r="212">
+    <row r="212" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B212" s="13"/>
     </row>
-    <row r="213">
+    <row r="213" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B213" s="13"/>
     </row>
-    <row r="214">
+    <row r="214" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B214" s="13"/>
     </row>
-    <row r="215">
+    <row r="215" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B215" s="13"/>
     </row>
-    <row r="216">
+    <row r="216" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B216" s="13"/>
     </row>
-    <row r="217">
+    <row r="217" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B217" s="13"/>
     </row>
-    <row r="218">
+    <row r="218" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B218" s="13"/>
     </row>
-    <row r="219">
+    <row r="219" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B219" s="13"/>
     </row>
-    <row r="220">
+    <row r="220" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B220" s="13"/>
     </row>
-    <row r="221">
+    <row r="221" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B221" s="13"/>
     </row>
-    <row r="222">
+    <row r="222" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B222" s="13"/>
     </row>
-    <row r="223">
+    <row r="223" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B223" s="13"/>
     </row>
-    <row r="224">
+    <row r="224" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B224" s="13"/>
     </row>
-    <row r="225">
+    <row r="225" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B225" s="13"/>
     </row>
-    <row r="226">
+    <row r="226" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B226" s="13"/>
     </row>
-    <row r="227">
+    <row r="227" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B227" s="13"/>
     </row>
-    <row r="228">
+    <row r="228" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B228" s="13"/>
     </row>
-    <row r="229">
+    <row r="229" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B229" s="13"/>
     </row>
-    <row r="230">
+    <row r="230" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B230" s="13"/>
     </row>
-    <row r="231">
+    <row r="231" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B231" s="13"/>
     </row>
-    <row r="232">
+    <row r="232" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B232" s="13"/>
     </row>
-    <row r="233">
+    <row r="233" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B233" s="13"/>
     </row>
-    <row r="234">
+    <row r="234" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B234" s="13"/>
     </row>
-    <row r="235">
+    <row r="235" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B235" s="13"/>
     </row>
-    <row r="236">
+    <row r="236" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B236" s="13"/>
     </row>
-    <row r="237">
+    <row r="237" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B237" s="13"/>
     </row>
-    <row r="238">
+    <row r="238" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B238" s="13"/>
     </row>
-    <row r="239">
+    <row r="239" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B239" s="13"/>
     </row>
-    <row r="240">
+    <row r="240" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B240" s="13"/>
     </row>
-    <row r="241">
+    <row r="241" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B241" s="13"/>
     </row>
-    <row r="242">
+    <row r="242" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B242" s="13"/>
     </row>
-    <row r="243">
+    <row r="243" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B243" s="13"/>
     </row>
-    <row r="244">
+    <row r="244" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B244" s="13"/>
     </row>
-    <row r="245">
+    <row r="245" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B245" s="13"/>
     </row>
-    <row r="246">
+    <row r="246" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B246" s="13"/>
     </row>
-    <row r="247">
+    <row r="247" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B247" s="13"/>
     </row>
-    <row r="248">
+    <row r="248" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B248" s="13"/>
     </row>
-    <row r="249">
+    <row r="249" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B249" s="13"/>
     </row>
-    <row r="250">
+    <row r="250" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B250" s="13"/>
     </row>
-    <row r="251">
+    <row r="251" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B251" s="13"/>
     </row>
-    <row r="252">
+    <row r="252" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B252" s="13"/>
     </row>
-    <row r="253">
+    <row r="253" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B253" s="13"/>
     </row>
-    <row r="254">
+    <row r="254" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B254" s="13"/>
     </row>
-    <row r="255">
+    <row r="255" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B255" s="13"/>
     </row>
-    <row r="256">
+    <row r="256" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B256" s="13"/>
     </row>
-    <row r="257">
+    <row r="257" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B257" s="13"/>
     </row>
-    <row r="258">
+    <row r="258" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B258" s="13"/>
     </row>
-    <row r="259">
+    <row r="259" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B259" s="13"/>
     </row>
-    <row r="260">
+    <row r="260" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B260" s="13"/>
     </row>
-    <row r="261">
+    <row r="261" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B261" s="13"/>
     </row>
-    <row r="262">
+    <row r="262" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B262" s="13"/>
     </row>
-    <row r="263">
+    <row r="263" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B263" s="13"/>
     </row>
-    <row r="264">
+    <row r="264" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B264" s="13"/>
     </row>
-    <row r="265">
+    <row r="265" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B265" s="13"/>
     </row>
-    <row r="266">
+    <row r="266" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B266" s="13"/>
     </row>
-    <row r="267">
+    <row r="267" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B267" s="13"/>
     </row>
-    <row r="268">
+    <row r="268" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B268" s="13"/>
     </row>
-    <row r="269">
+    <row r="269" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B269" s="13"/>
     </row>
-    <row r="270">
+    <row r="270" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B270" s="13"/>
     </row>
-    <row r="271">
+    <row r="271" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B271" s="13"/>
     </row>
-    <row r="272">
+    <row r="272" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B272" s="13"/>
     </row>
-    <row r="273">
+    <row r="273" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B273" s="13"/>
     </row>
-    <row r="274">
+    <row r="274" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B274" s="13"/>
     </row>
-    <row r="275">
+    <row r="275" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B275" s="13"/>
     </row>
-    <row r="276">
+    <row r="276" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B276" s="13"/>
     </row>
-    <row r="277">
+    <row r="277" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B277" s="13"/>
     </row>
-    <row r="278">
+    <row r="278" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B278" s="13"/>
     </row>
-    <row r="279">
+    <row r="279" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B279" s="13"/>
     </row>
-    <row r="280">
+    <row r="280" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B280" s="13"/>
     </row>
-    <row r="281">
+    <row r="281" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B281" s="13"/>
     </row>
-    <row r="282">
+    <row r="282" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B282" s="13"/>
     </row>
-    <row r="283">
+    <row r="283" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B283" s="13"/>
     </row>
-    <row r="284">
+    <row r="284" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B284" s="13"/>
     </row>
-    <row r="285">
+    <row r="285" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B285" s="13"/>
     </row>
-    <row r="286">
+    <row r="286" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B286" s="13"/>
     </row>
-    <row r="287">
+    <row r="287" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B287" s="13"/>
     </row>
-    <row r="288">
+    <row r="288" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B288" s="13"/>
     </row>
-    <row r="289">
+    <row r="289" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B289" s="13"/>
     </row>
-    <row r="290">
+    <row r="290" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B290" s="13"/>
     </row>
-    <row r="291">
+    <row r="291" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B291" s="13"/>
     </row>
-    <row r="292">
+    <row r="292" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B292" s="13"/>
     </row>
-    <row r="293">
+    <row r="293" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B293" s="13"/>
     </row>
-    <row r="294">
+    <row r="294" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B294" s="13"/>
     </row>
-    <row r="295">
+    <row r="295" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B295" s="13"/>
     </row>
-    <row r="296">
+    <row r="296" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B296" s="13"/>
     </row>
-    <row r="297">
+    <row r="297" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B297" s="13"/>
     </row>
-    <row r="298">
+    <row r="298" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B298" s="13"/>
     </row>
-    <row r="299">
+    <row r="299" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B299" s="13"/>
     </row>
-    <row r="300">
+    <row r="300" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B300" s="13"/>
     </row>
-    <row r="301">
+    <row r="301" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B301" s="13"/>
     </row>
-    <row r="302">
+    <row r="302" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B302" s="13"/>
     </row>
-    <row r="303">
+    <row r="303" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B303" s="13"/>
     </row>
-    <row r="304">
+    <row r="304" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B304" s="13"/>
     </row>
-    <row r="305">
+    <row r="305" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B305" s="13"/>
     </row>
-    <row r="306">
+    <row r="306" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B306" s="13"/>
     </row>
-    <row r="307">
+    <row r="307" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B307" s="13"/>
     </row>
-    <row r="308">
+    <row r="308" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B308" s="13"/>
     </row>
-    <row r="309">
+    <row r="309" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B309" s="13"/>
     </row>
-    <row r="310">
+    <row r="310" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B310" s="13"/>
     </row>
-    <row r="311">
+    <row r="311" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B311" s="13"/>
     </row>
-    <row r="312">
+    <row r="312" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B312" s="13"/>
     </row>
-    <row r="313">
+    <row r="313" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B313" s="13"/>
     </row>
-    <row r="314">
+    <row r="314" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B314" s="13"/>
     </row>
-    <row r="315">
+    <row r="315" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B315" s="13"/>
     </row>
-    <row r="316">
+    <row r="316" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B316" s="13"/>
     </row>
-    <row r="317">
+    <row r="317" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B317" s="13"/>
     </row>
-    <row r="318">
+    <row r="318" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B318" s="13"/>
     </row>
-    <row r="319">
+    <row r="319" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B319" s="13"/>
     </row>
-    <row r="320">
+    <row r="320" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B320" s="13"/>
     </row>
-    <row r="321">
+    <row r="321" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B321" s="13"/>
     </row>
-    <row r="322">
+    <row r="322" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B322" s="13"/>
     </row>
-    <row r="323">
+    <row r="323" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B323" s="13"/>
     </row>
-    <row r="324">
+    <row r="324" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B324" s="13"/>
     </row>
-    <row r="325">
+    <row r="325" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B325" s="13"/>
     </row>
-    <row r="326">
+    <row r="326" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B326" s="13"/>
     </row>
-    <row r="327">
+    <row r="327" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B327" s="13"/>
     </row>
-    <row r="328">
+    <row r="328" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B328" s="13"/>
     </row>
-    <row r="329">
+    <row r="329" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B329" s="13"/>
     </row>
-    <row r="330">
+    <row r="330" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B330" s="13"/>
     </row>
-    <row r="331">
+    <row r="331" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B331" s="13"/>
     </row>
-    <row r="332">
+    <row r="332" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B332" s="13"/>
     </row>
-    <row r="333">
+    <row r="333" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B333" s="13"/>
     </row>
-    <row r="334">
+    <row r="334" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B334" s="13"/>
     </row>
-    <row r="335">
+    <row r="335" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B335" s="13"/>
     </row>
-    <row r="336">
+    <row r="336" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B336" s="13"/>
     </row>
-    <row r="337">
+    <row r="337" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B337" s="13"/>
     </row>
-    <row r="338">
+    <row r="338" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B338" s="13"/>
     </row>
-    <row r="339">
+    <row r="339" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B339" s="13"/>
     </row>
-    <row r="340">
+    <row r="340" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B340" s="13"/>
     </row>
-    <row r="341">
+    <row r="341" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B341" s="13"/>
     </row>
-    <row r="342">
+    <row r="342" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B342" s="13"/>
     </row>
-    <row r="343">
+    <row r="343" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B343" s="13"/>
     </row>
-    <row r="344">
+    <row r="344" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B344" s="13"/>
     </row>
-    <row r="345">
+    <row r="345" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B345" s="13"/>
     </row>
-    <row r="346">
+    <row r="346" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B346" s="13"/>
     </row>
-    <row r="347">
+    <row r="347" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B347" s="13"/>
     </row>
-    <row r="348">
+    <row r="348" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B348" s="13"/>
     </row>
-    <row r="349">
+    <row r="349" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B349" s="13"/>
     </row>
-    <row r="350">
+    <row r="350" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B350" s="13"/>
     </row>
-    <row r="351">
+    <row r="351" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B351" s="13"/>
     </row>
-    <row r="352">
+    <row r="352" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B352" s="13"/>
     </row>
-    <row r="353">
+    <row r="353" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B353" s="13"/>
     </row>
-    <row r="354">
+    <row r="354" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B354" s="13"/>
     </row>
-    <row r="355">
+    <row r="355" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B355" s="13"/>
     </row>
-    <row r="356">
+    <row r="356" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B356" s="13"/>
     </row>
-    <row r="357">
+    <row r="357" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B357" s="13"/>
     </row>
-    <row r="358">
+    <row r="358" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B358" s="13"/>
     </row>
-    <row r="359">
+    <row r="359" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B359" s="13"/>
     </row>
-    <row r="360">
+    <row r="360" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B360" s="13"/>
     </row>
-    <row r="361">
+    <row r="361" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B361" s="13"/>
     </row>
-    <row r="362">
+    <row r="362" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B362" s="13"/>
     </row>
-    <row r="363">
+    <row r="363" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B363" s="13"/>
     </row>
-    <row r="364">
+    <row r="364" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B364" s="13"/>
     </row>
-    <row r="365">
+    <row r="365" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B365" s="13"/>
     </row>
-    <row r="366">
+    <row r="366" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B366" s="13"/>
     </row>
-    <row r="367">
+    <row r="367" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B367" s="13"/>
     </row>
-    <row r="368">
+    <row r="368" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B368" s="13"/>
     </row>
-    <row r="369">
+    <row r="369" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B369" s="13"/>
     </row>
-    <row r="370">
+    <row r="370" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B370" s="13"/>
     </row>
-    <row r="371">
+    <row r="371" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B371" s="13"/>
     </row>
-    <row r="372">
+    <row r="372" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B372" s="13"/>
     </row>
-    <row r="373">
+    <row r="373" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B373" s="13"/>
     </row>
-    <row r="374">
+    <row r="374" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B374" s="13"/>
     </row>
-    <row r="375">
+    <row r="375" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B375" s="13"/>
     </row>
-    <row r="376">
+    <row r="376" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B376" s="13"/>
     </row>
-    <row r="377">
+    <row r="377" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B377" s="13"/>
     </row>
-    <row r="378">
+    <row r="378" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B378" s="13"/>
     </row>
-    <row r="379">
+    <row r="379" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B379" s="13"/>
     </row>
-    <row r="380">
+    <row r="380" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B380" s="13"/>
     </row>
-    <row r="381">
+    <row r="381" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B381" s="13"/>
     </row>
-    <row r="382">
+    <row r="382" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B382" s="13"/>
     </row>
-    <row r="383">
+    <row r="383" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B383" s="13"/>
     </row>
-    <row r="384">
+    <row r="384" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B384" s="13"/>
     </row>
-    <row r="385">
+    <row r="385" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B385" s="13"/>
     </row>
-    <row r="386">
+    <row r="386" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B386" s="13"/>
     </row>
-    <row r="387">
+    <row r="387" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B387" s="13"/>
     </row>
-    <row r="388">
+    <row r="388" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B388" s="13"/>
     </row>
-    <row r="389">
+    <row r="389" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B389" s="13"/>
     </row>
-    <row r="390">
+    <row r="390" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B390" s="13"/>
     </row>
-    <row r="391">
+    <row r="391" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B391" s="13"/>
     </row>
-    <row r="392">
+    <row r="392" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B392" s="13"/>
     </row>
-    <row r="393">
+    <row r="393" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B393" s="13"/>
     </row>
-    <row r="394">
+    <row r="394" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B394" s="13"/>
     </row>
-    <row r="395">
+    <row r="395" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B395" s="13"/>
     </row>
-    <row r="396">
+    <row r="396" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B396" s="13"/>
     </row>
-    <row r="397">
+    <row r="397" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B397" s="13"/>
     </row>
-    <row r="398">
+    <row r="398" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B398" s="13"/>
     </row>
-    <row r="399">
+    <row r="399" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B399" s="13"/>
     </row>
-    <row r="400">
+    <row r="400" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B400" s="13"/>
     </row>
-    <row r="401">
+    <row r="401" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B401" s="13"/>
     </row>
-    <row r="402">
+    <row r="402" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B402" s="13"/>
     </row>
-    <row r="403">
+    <row r="403" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B403" s="13"/>
     </row>
-    <row r="404">
+    <row r="404" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B404" s="13"/>
     </row>
-    <row r="405">
+    <row r="405" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B405" s="13"/>
     </row>
-    <row r="406">
+    <row r="406" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B406" s="13"/>
     </row>
-    <row r="407">
+    <row r="407" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B407" s="13"/>
     </row>
-    <row r="408">
+    <row r="408" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B408" s="13"/>
     </row>
-    <row r="409">
+    <row r="409" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B409" s="13"/>
     </row>
-    <row r="410">
+    <row r="410" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B410" s="13"/>
     </row>
-    <row r="411">
+    <row r="411" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B411" s="13"/>
     </row>
-    <row r="412">
+    <row r="412" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B412" s="13"/>
     </row>
-    <row r="413">
+    <row r="413" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B413" s="13"/>
     </row>
-    <row r="414">
+    <row r="414" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B414" s="13"/>
     </row>
-    <row r="415">
+    <row r="415" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B415" s="13"/>
     </row>
-    <row r="416">
+    <row r="416" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B416" s="13"/>
     </row>
-    <row r="417">
+    <row r="417" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B417" s="13"/>
     </row>
-    <row r="418">
+    <row r="418" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B418" s="13"/>
     </row>
-    <row r="419">
+    <row r="419" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B419" s="13"/>
     </row>
-    <row r="420">
+    <row r="420" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B420" s="13"/>
     </row>
-    <row r="421">
+    <row r="421" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B421" s="13"/>
     </row>
-    <row r="422">
+    <row r="422" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B422" s="13"/>
     </row>
-    <row r="423">
+    <row r="423" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B423" s="13"/>
     </row>
-    <row r="424">
+    <row r="424" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B424" s="13"/>
     </row>
-    <row r="425">
+    <row r="425" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B425" s="13"/>
     </row>
-    <row r="426">
+    <row r="426" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B426" s="13"/>
     </row>
-    <row r="427">
+    <row r="427" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B427" s="13"/>
     </row>
-    <row r="428">
+    <row r="428" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B428" s="13"/>
     </row>
-    <row r="429">
+    <row r="429" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B429" s="13"/>
     </row>
-    <row r="430">
+    <row r="430" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B430" s="13"/>
     </row>
-    <row r="431">
+    <row r="431" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B431" s="13"/>
     </row>
-    <row r="432">
+    <row r="432" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B432" s="13"/>
     </row>
-    <row r="433">
+    <row r="433" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B433" s="13"/>
     </row>
-    <row r="434">
+    <row r="434" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B434" s="13"/>
     </row>
-    <row r="435">
+    <row r="435" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B435" s="13"/>
     </row>
-    <row r="436">
+    <row r="436" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B436" s="13"/>
     </row>
-    <row r="437">
+    <row r="437" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B437" s="13"/>
     </row>
-    <row r="438">
+    <row r="438" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B438" s="13"/>
     </row>
-    <row r="439">
+    <row r="439" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B439" s="13"/>
     </row>
-    <row r="440">
+    <row r="440" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B440" s="13"/>
     </row>
-    <row r="441">
+    <row r="441" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B441" s="13"/>
     </row>
-    <row r="442">
+    <row r="442" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B442" s="13"/>
     </row>
-    <row r="443">
+    <row r="443" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B443" s="13"/>
     </row>
-    <row r="444">
+    <row r="444" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B444" s="13"/>
     </row>
-    <row r="445">
+    <row r="445" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B445" s="13"/>
     </row>
-    <row r="446">
+    <row r="446" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B446" s="13"/>
     </row>
-    <row r="447">
+    <row r="447" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B447" s="13"/>
     </row>
-    <row r="448">
+    <row r="448" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B448" s="13"/>
     </row>
-    <row r="449">
+    <row r="449" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B449" s="13"/>
     </row>
-    <row r="450">
+    <row r="450" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B450" s="13"/>
     </row>
-    <row r="451">
+    <row r="451" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B451" s="13"/>
     </row>
-    <row r="452">
+    <row r="452" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B452" s="13"/>
     </row>
-    <row r="453">
+    <row r="453" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B453" s="13"/>
     </row>
-    <row r="454">
+    <row r="454" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B454" s="13"/>
     </row>
-    <row r="455">
+    <row r="455" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B455" s="13"/>
     </row>
-    <row r="456">
+    <row r="456" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B456" s="13"/>
     </row>
-    <row r="457">
+    <row r="457" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B457" s="13"/>
     </row>
-    <row r="458">
+    <row r="458" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B458" s="13"/>
     </row>
-    <row r="459">
+    <row r="459" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B459" s="13"/>
     </row>
-    <row r="460">
+    <row r="460" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B460" s="13"/>
     </row>
-    <row r="461">
+    <row r="461" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B461" s="13"/>
     </row>
-    <row r="462">
+    <row r="462" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B462" s="13"/>
     </row>
-    <row r="463">
+    <row r="463" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B463" s="13"/>
     </row>
-    <row r="464">
+    <row r="464" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B464" s="13"/>
     </row>
-    <row r="465">
+    <row r="465" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B465" s="13"/>
     </row>
-    <row r="466">
+    <row r="466" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B466" s="13"/>
     </row>
-    <row r="467">
+    <row r="467" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B467" s="13"/>
     </row>
-    <row r="468">
+    <row r="468" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B468" s="13"/>
     </row>
-    <row r="469">
+    <row r="469" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B469" s="13"/>
     </row>
-    <row r="470">
+    <row r="470" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B470" s="13"/>
     </row>
-    <row r="471">
+    <row r="471" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B471" s="13"/>
     </row>
-    <row r="472">
+    <row r="472" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B472" s="13"/>
     </row>
-    <row r="473">
+    <row r="473" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B473" s="13"/>
     </row>
-    <row r="474">
+    <row r="474" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B474" s="13"/>
     </row>
-    <row r="475">
+    <row r="475" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B475" s="13"/>
     </row>
-    <row r="476">
+    <row r="476" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B476" s="13"/>
     </row>
-    <row r="477">
+    <row r="477" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B477" s="13"/>
     </row>
-    <row r="478">
+    <row r="478" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B478" s="13"/>
     </row>
-    <row r="479">
+    <row r="479" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B479" s="13"/>
     </row>
-    <row r="480">
+    <row r="480" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B480" s="13"/>
     </row>
-    <row r="481">
+    <row r="481" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B481" s="13"/>
     </row>
-    <row r="482">
+    <row r="482" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B482" s="13"/>
     </row>
-    <row r="483">
+    <row r="483" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B483" s="13"/>
     </row>
-    <row r="484">
+    <row r="484" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B484" s="13"/>
     </row>
-    <row r="485">
+    <row r="485" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B485" s="13"/>
     </row>
-    <row r="486">
+    <row r="486" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B486" s="13"/>
     </row>
-    <row r="487">
+    <row r="487" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B487" s="13"/>
     </row>
-    <row r="488">
+    <row r="488" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B488" s="13"/>
     </row>
-    <row r="489">
+    <row r="489" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B489" s="13"/>
     </row>
-    <row r="490">
+    <row r="490" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B490" s="13"/>
     </row>
-    <row r="491">
+    <row r="491" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B491" s="13"/>
     </row>
-    <row r="492">
+    <row r="492" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B492" s="13"/>
     </row>
-    <row r="493">
+    <row r="493" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B493" s="13"/>
     </row>
-    <row r="494">
+    <row r="494" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B494" s="13"/>
     </row>
-    <row r="495">
+    <row r="495" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B495" s="13"/>
     </row>
-    <row r="496">
+    <row r="496" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B496" s="13"/>
     </row>
-    <row r="497">
+    <row r="497" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B497" s="13"/>
     </row>
-    <row r="498">
+    <row r="498" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B498" s="13"/>
     </row>
-    <row r="499">
+    <row r="499" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B499" s="13"/>
     </row>
-    <row r="500">
+    <row r="500" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B500" s="13"/>
     </row>
-    <row r="501">
+    <row r="501" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B501" s="13"/>
     </row>
-    <row r="502">
+    <row r="502" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B502" s="13"/>
     </row>
-    <row r="503">
+    <row r="503" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B503" s="13"/>
     </row>
-    <row r="504">
+    <row r="504" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B504" s="13"/>
     </row>
-    <row r="505">
+    <row r="505" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B505" s="13"/>
     </row>
-    <row r="506">
+    <row r="506" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B506" s="13"/>
     </row>
-    <row r="507">
+    <row r="507" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B507" s="13"/>
     </row>
-    <row r="508">
+    <row r="508" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B508" s="13"/>
     </row>
-    <row r="509">
+    <row r="509" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B509" s="13"/>
     </row>
-    <row r="510">
+    <row r="510" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B510" s="13"/>
     </row>
-    <row r="511">
+    <row r="511" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B511" s="13"/>
     </row>
-    <row r="512">
+    <row r="512" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B512" s="13"/>
     </row>
-    <row r="513">
+    <row r="513" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B513" s="13"/>
     </row>
-    <row r="514">
+    <row r="514" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B514" s="13"/>
     </row>
-    <row r="515">
+    <row r="515" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B515" s="13"/>
     </row>
-    <row r="516">
+    <row r="516" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B516" s="13"/>
     </row>
-    <row r="517">
+    <row r="517" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B517" s="13"/>
     </row>
-    <row r="518">
+    <row r="518" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B518" s="13"/>
     </row>
-    <row r="519">
+    <row r="519" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B519" s="13"/>
     </row>
-    <row r="520">
+    <row r="520" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B520" s="13"/>
     </row>
-    <row r="521">
+    <row r="521" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B521" s="13"/>
     </row>
-    <row r="522">
+    <row r="522" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B522" s="13"/>
     </row>
-    <row r="523">
+    <row r="523" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B523" s="13"/>
     </row>
-    <row r="524">
+    <row r="524" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B524" s="13"/>
     </row>
-    <row r="525">
+    <row r="525" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B525" s="13"/>
     </row>
-    <row r="526">
+    <row r="526" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B526" s="13"/>
     </row>
-    <row r="527">
+    <row r="527" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B527" s="13"/>
     </row>
-    <row r="528">
+    <row r="528" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B528" s="13"/>
     </row>
-    <row r="529">
+    <row r="529" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B529" s="13"/>
     </row>
-    <row r="530">
+    <row r="530" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B530" s="13"/>
     </row>
-    <row r="531">
+    <row r="531" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B531" s="13"/>
     </row>
-    <row r="532">
+    <row r="532" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B532" s="13"/>
     </row>
-    <row r="533">
+    <row r="533" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B533" s="13"/>
     </row>
-    <row r="534">
+    <row r="534" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B534" s="13"/>
     </row>
-    <row r="535">
+    <row r="535" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B535" s="13"/>
     </row>
-    <row r="536">
+    <row r="536" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B536" s="13"/>
     </row>
-    <row r="537">
+    <row r="537" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B537" s="13"/>
     </row>
-    <row r="538">
+    <row r="538" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B538" s="13"/>
     </row>
-    <row r="539">
+    <row r="539" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B539" s="13"/>
     </row>
-    <row r="540">
+    <row r="540" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B540" s="13"/>
     </row>
-    <row r="541">
+    <row r="541" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B541" s="13"/>
     </row>
-    <row r="542">
+    <row r="542" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B542" s="13"/>
     </row>
-    <row r="543">
+    <row r="543" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B543" s="13"/>
     </row>
-    <row r="544">
+    <row r="544" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B544" s="13"/>
     </row>
-    <row r="545">
+    <row r="545" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B545" s="13"/>
     </row>
-    <row r="546">
+    <row r="546" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B546" s="13"/>
     </row>
-    <row r="547">
+    <row r="547" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B547" s="13"/>
     </row>
-    <row r="548">
+    <row r="548" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B548" s="13"/>
     </row>
-    <row r="549">
+    <row r="549" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B549" s="13"/>
     </row>
-    <row r="550">
+    <row r="550" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B550" s="13"/>
     </row>
-    <row r="551">
+    <row r="551" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B551" s="13"/>
     </row>
-    <row r="552">
+    <row r="552" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B552" s="13"/>
     </row>
-    <row r="553">
+    <row r="553" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B553" s="13"/>
     </row>
-    <row r="554">
+    <row r="554" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B554" s="13"/>
     </row>
-    <row r="555">
+    <row r="555" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B555" s="13"/>
     </row>
-    <row r="556">
+    <row r="556" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B556" s="13"/>
     </row>
-    <row r="557">
+    <row r="557" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B557" s="13"/>
     </row>
-    <row r="558">
+    <row r="558" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B558" s="13"/>
     </row>
-    <row r="559">
+    <row r="559" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B559" s="13"/>
     </row>
-    <row r="560">
+    <row r="560" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B560" s="13"/>
     </row>
-    <row r="561">
+    <row r="561" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B561" s="13"/>
     </row>
-    <row r="562">
+    <row r="562" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B562" s="13"/>
     </row>
-    <row r="563">
+    <row r="563" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B563" s="13"/>
     </row>
-    <row r="564">
+    <row r="564" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B564" s="13"/>
     </row>
-    <row r="565">
+    <row r="565" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B565" s="13"/>
     </row>
-    <row r="566">
+    <row r="566" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B566" s="13"/>
     </row>
-    <row r="567">
+    <row r="567" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B567" s="13"/>
     </row>
-    <row r="568">
+    <row r="568" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B568" s="13"/>
     </row>
-    <row r="569">
+    <row r="569" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B569" s="13"/>
     </row>
-    <row r="570">
+    <row r="570" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B570" s="13"/>
     </row>
-    <row r="571">
+    <row r="571" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B571" s="13"/>
     </row>
-    <row r="572">
+    <row r="572" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B572" s="13"/>
     </row>
-    <row r="573">
+    <row r="573" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B573" s="13"/>
     </row>
-    <row r="574">
+    <row r="574" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B574" s="13"/>
     </row>
-    <row r="575">
+    <row r="575" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B575" s="13"/>
     </row>
-    <row r="576">
+    <row r="576" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B576" s="13"/>
     </row>
-    <row r="577">
+    <row r="577" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B577" s="13"/>
     </row>
-    <row r="578">
+    <row r="578" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B578" s="13"/>
     </row>
-    <row r="579">
+    <row r="579" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B579" s="13"/>
     </row>
-    <row r="580">
+    <row r="580" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B580" s="13"/>
     </row>
-    <row r="581">
+    <row r="581" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B581" s="13"/>
     </row>
-    <row r="582">
+    <row r="582" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B582" s="13"/>
     </row>
-    <row r="583">
+    <row r="583" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B583" s="13"/>
     </row>
-    <row r="584">
+    <row r="584" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B584" s="13"/>
     </row>
-    <row r="585">
+    <row r="585" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B585" s="13"/>
     </row>
-    <row r="586">
+    <row r="586" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B586" s="13"/>
     </row>
-    <row r="587">
+    <row r="587" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B587" s="13"/>
     </row>
-    <row r="588">
+    <row r="588" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B588" s="13"/>
     </row>
-    <row r="589">
+    <row r="589" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B589" s="13"/>
     </row>
-    <row r="590">
+    <row r="590" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B590" s="13"/>
     </row>
-    <row r="591">
+    <row r="591" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B591" s="13"/>
     </row>
-    <row r="592">
+    <row r="592" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B592" s="13"/>
     </row>
-    <row r="593">
+    <row r="593" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B593" s="13"/>
     </row>
-    <row r="594">
+    <row r="594" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B594" s="13"/>
     </row>
-    <row r="595">
+    <row r="595" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B595" s="13"/>
     </row>
-    <row r="596">
+    <row r="596" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B596" s="13"/>
     </row>
-    <row r="597">
+    <row r="597" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B597" s="13"/>
     </row>
-    <row r="598">
+    <row r="598" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B598" s="13"/>
     </row>
-    <row r="599">
+    <row r="599" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B599" s="13"/>
     </row>
-    <row r="600">
+    <row r="600" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B600" s="13"/>
     </row>
-    <row r="601">
+    <row r="601" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B601" s="13"/>
     </row>
-    <row r="602">
+    <row r="602" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B602" s="13"/>
     </row>
-    <row r="603">
+    <row r="603" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B603" s="13"/>
     </row>
-    <row r="604">
+    <row r="604" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B604" s="13"/>
     </row>
-    <row r="605">
+    <row r="605" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B605" s="13"/>
     </row>
-    <row r="606">
+    <row r="606" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B606" s="13"/>
     </row>
-    <row r="607">
+    <row r="607" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B607" s="13"/>
     </row>
-    <row r="608">
+    <row r="608" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B608" s="13"/>
     </row>
-    <row r="609">
+    <row r="609" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B609" s="13"/>
     </row>
-    <row r="610">
+    <row r="610" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B610" s="13"/>
     </row>
-    <row r="611">
+    <row r="611" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B611" s="13"/>
     </row>
-    <row r="612">
+    <row r="612" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B612" s="13"/>
     </row>
-    <row r="613">
+    <row r="613" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B613" s="13"/>
     </row>
-    <row r="614">
+    <row r="614" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B614" s="13"/>
     </row>
-    <row r="615">
+    <row r="615" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B615" s="13"/>
     </row>
-    <row r="616">
+    <row r="616" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B616" s="13"/>
     </row>
-    <row r="617">
+    <row r="617" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B617" s="13"/>
     </row>
-    <row r="618">
+    <row r="618" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B618" s="13"/>
     </row>
-    <row r="619">
+    <row r="619" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B619" s="13"/>
     </row>
-    <row r="620">
+    <row r="620" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B620" s="13"/>
     </row>
-    <row r="621">
+    <row r="621" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B621" s="13"/>
     </row>
-    <row r="622">
+    <row r="622" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B622" s="13"/>
     </row>
-    <row r="623">
+    <row r="623" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B623" s="13"/>
     </row>
-    <row r="624">
+    <row r="624" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B624" s="13"/>
     </row>
-    <row r="625">
+    <row r="625" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B625" s="13"/>
     </row>
-    <row r="626">
+    <row r="626" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B626" s="13"/>
     </row>
-    <row r="627">
+    <row r="627" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B627" s="13"/>
     </row>
-    <row r="628">
+    <row r="628" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B628" s="13"/>
     </row>
-    <row r="629">
+    <row r="629" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B629" s="13"/>
     </row>
-    <row r="630">
+    <row r="630" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B630" s="13"/>
     </row>
-    <row r="631">
+    <row r="631" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B631" s="13"/>
     </row>
-    <row r="632">
+    <row r="632" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B632" s="13"/>
     </row>
-    <row r="633">
+    <row r="633" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B633" s="13"/>
     </row>
-    <row r="634">
+    <row r="634" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B634" s="13"/>
     </row>
-    <row r="635">
+    <row r="635" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B635" s="13"/>
     </row>
-    <row r="636">
+    <row r="636" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B636" s="13"/>
     </row>
-    <row r="637">
+    <row r="637" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B637" s="13"/>
     </row>
-    <row r="638">
+    <row r="638" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B638" s="13"/>
     </row>
-    <row r="639">
+    <row r="639" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B639" s="13"/>
     </row>
-    <row r="640">
+    <row r="640" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B640" s="13"/>
     </row>
-    <row r="641">
+    <row r="641" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B641" s="13"/>
     </row>
-    <row r="642">
+    <row r="642" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B642" s="13"/>
     </row>
-    <row r="643">
+    <row r="643" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B643" s="13"/>
     </row>
-    <row r="644">
+    <row r="644" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B644" s="13"/>
     </row>
-    <row r="645">
+    <row r="645" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B645" s="13"/>
     </row>
-    <row r="646">
+    <row r="646" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B646" s="13"/>
     </row>
-    <row r="647">
+    <row r="647" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B647" s="13"/>
     </row>
-    <row r="648">
+    <row r="648" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B648" s="13"/>
     </row>
-    <row r="649">
+    <row r="649" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B649" s="13"/>
     </row>
-    <row r="650">
+    <row r="650" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B650" s="13"/>
     </row>
-    <row r="651">
+    <row r="651" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B651" s="13"/>
     </row>
-    <row r="652">
+    <row r="652" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B652" s="13"/>
     </row>
-    <row r="653">
+    <row r="653" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B653" s="13"/>
     </row>
-    <row r="654">
+    <row r="654" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B654" s="13"/>
     </row>
-    <row r="655">
+    <row r="655" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B655" s="13"/>
     </row>
-    <row r="656">
+    <row r="656" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B656" s="13"/>
     </row>
-    <row r="657">
+    <row r="657" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B657" s="13"/>
     </row>
-    <row r="658">
+    <row r="658" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B658" s="13"/>
     </row>
-    <row r="659">
+    <row r="659" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B659" s="13"/>
     </row>
-    <row r="660">
+    <row r="660" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B660" s="13"/>
     </row>
-    <row r="661">
+    <row r="661" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B661" s="13"/>
     </row>
-    <row r="662">
+    <row r="662" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B662" s="13"/>
     </row>
-    <row r="663">
+    <row r="663" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B663" s="13"/>
     </row>
-    <row r="664">
+    <row r="664" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B664" s="13"/>
     </row>
-    <row r="665">
+    <row r="665" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B665" s="13"/>
     </row>
-    <row r="666">
+    <row r="666" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B666" s="13"/>
     </row>
-    <row r="667">
+    <row r="667" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B667" s="13"/>
     </row>
-    <row r="668">
+    <row r="668" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B668" s="13"/>
     </row>
-    <row r="669">
+    <row r="669" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B669" s="13"/>
     </row>
-    <row r="670">
+    <row r="670" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B670" s="13"/>
     </row>
-    <row r="671">
+    <row r="671" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B671" s="13"/>
     </row>
-    <row r="672">
+    <row r="672" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B672" s="13"/>
     </row>
-    <row r="673">
+    <row r="673" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B673" s="13"/>
     </row>
-    <row r="674">
+    <row r="674" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B674" s="13"/>
     </row>
-    <row r="675">
+    <row r="675" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B675" s="13"/>
     </row>
-    <row r="676">
+    <row r="676" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B676" s="13"/>
     </row>
-    <row r="677">
+    <row r="677" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B677" s="13"/>
     </row>
-    <row r="678">
+    <row r="678" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B678" s="13"/>
     </row>
-    <row r="679">
+    <row r="679" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B679" s="13"/>
     </row>
-    <row r="680">
+    <row r="680" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B680" s="13"/>
     </row>
-    <row r="681">
+    <row r="681" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B681" s="13"/>
     </row>
-    <row r="682">
+    <row r="682" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B682" s="13"/>
     </row>
-    <row r="683">
+    <row r="683" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B683" s="13"/>
     </row>
-    <row r="684">
+    <row r="684" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B684" s="13"/>
     </row>
-    <row r="685">
+    <row r="685" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B685" s="13"/>
     </row>
-    <row r="686">
+    <row r="686" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B686" s="13"/>
     </row>
-    <row r="687">
+    <row r="687" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B687" s="13"/>
     </row>
-    <row r="688">
+    <row r="688" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B688" s="13"/>
     </row>
-    <row r="689">
+    <row r="689" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B689" s="13"/>
     </row>
-    <row r="690">
+    <row r="690" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B690" s="13"/>
     </row>
-    <row r="691">
+    <row r="691" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B691" s="13"/>
     </row>
-    <row r="692">
+    <row r="692" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B692" s="13"/>
     </row>
-    <row r="693">
+    <row r="693" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B693" s="13"/>
     </row>
-    <row r="694">
+    <row r="694" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B694" s="13"/>
     </row>
-    <row r="695">
+    <row r="695" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B695" s="13"/>
     </row>
-    <row r="696">
+    <row r="696" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B696" s="13"/>
     </row>
-    <row r="697">
+    <row r="697" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B697" s="13"/>
     </row>
-    <row r="698">
+    <row r="698" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B698" s="13"/>
     </row>
-    <row r="699">
+    <row r="699" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B699" s="13"/>
     </row>
-    <row r="700">
+    <row r="700" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B700" s="13"/>
     </row>
-    <row r="701">
+    <row r="701" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B701" s="13"/>
     </row>
-    <row r="702">
+    <row r="702" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B702" s="13"/>
     </row>
-    <row r="703">
+    <row r="703" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B703" s="13"/>
     </row>
-    <row r="704">
+    <row r="704" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B704" s="13"/>
     </row>
-    <row r="705">
+    <row r="705" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B705" s="13"/>
     </row>
-    <row r="706">
+    <row r="706" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B706" s="13"/>
     </row>
-    <row r="707">
+    <row r="707" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B707" s="13"/>
     </row>
-    <row r="708">
+    <row r="708" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B708" s="13"/>
     </row>
-    <row r="709">
+    <row r="709" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B709" s="13"/>
     </row>
-    <row r="710">
+    <row r="710" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B710" s="13"/>
     </row>
-    <row r="711">
+    <row r="711" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B711" s="13"/>
     </row>
-    <row r="712">
+    <row r="712" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B712" s="13"/>
     </row>
-    <row r="713">
+    <row r="713" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B713" s="13"/>
     </row>
-    <row r="714">
+    <row r="714" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B714" s="13"/>
     </row>
-    <row r="715">
+    <row r="715" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B715" s="13"/>
     </row>
-    <row r="716">
+    <row r="716" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B716" s="13"/>
     </row>
-    <row r="717">
+    <row r="717" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B717" s="13"/>
     </row>
-    <row r="718">
+    <row r="718" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B718" s="13"/>
     </row>
-    <row r="719">
+    <row r="719" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B719" s="13"/>
     </row>
-    <row r="720">
+    <row r="720" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B720" s="13"/>
     </row>
-    <row r="721">
+    <row r="721" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B721" s="13"/>
     </row>
-    <row r="722">
+    <row r="722" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B722" s="13"/>
     </row>
-    <row r="723">
+    <row r="723" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B723" s="13"/>
     </row>
-    <row r="724">
+    <row r="724" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B724" s="13"/>
     </row>
-    <row r="725">
+    <row r="725" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B725" s="13"/>
     </row>
-    <row r="726">
+    <row r="726" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B726" s="13"/>
     </row>
-    <row r="727">
+    <row r="727" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B727" s="13"/>
     </row>
-    <row r="728">
+    <row r="728" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B728" s="13"/>
     </row>
-    <row r="729">
+    <row r="729" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B729" s="13"/>
     </row>
-    <row r="730">
+    <row r="730" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B730" s="13"/>
     </row>
-    <row r="731">
+    <row r="731" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B731" s="13"/>
     </row>
-    <row r="732">
+    <row r="732" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B732" s="13"/>
     </row>
-    <row r="733">
+    <row r="733" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B733" s="13"/>
     </row>
-    <row r="734">
+    <row r="734" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B734" s="13"/>
     </row>
-    <row r="735">
+    <row r="735" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B735" s="13"/>
     </row>
-    <row r="736">
+    <row r="736" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B736" s="13"/>
     </row>
-    <row r="737">
+    <row r="737" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B737" s="13"/>
     </row>
-    <row r="738">
+    <row r="738" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B738" s="13"/>
     </row>
-    <row r="739">
+    <row r="739" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B739" s="13"/>
     </row>
-    <row r="740">
+    <row r="740" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B740" s="13"/>
     </row>
-    <row r="741">
+    <row r="741" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B741" s="13"/>
     </row>
-    <row r="742">
+    <row r="742" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B742" s="13"/>
     </row>
-    <row r="743">
+    <row r="743" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B743" s="13"/>
     </row>
-    <row r="744">
+    <row r="744" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B744" s="13"/>
     </row>
-    <row r="745">
+    <row r="745" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B745" s="13"/>
     </row>
-    <row r="746">
+    <row r="746" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B746" s="13"/>
     </row>
-    <row r="747">
+    <row r="747" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B747" s="13"/>
     </row>
-    <row r="748">
+    <row r="748" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B748" s="13"/>
     </row>
-    <row r="749">
+    <row r="749" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B749" s="13"/>
     </row>
-    <row r="750">
+    <row r="750" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B750" s="13"/>
     </row>
-    <row r="751">
+    <row r="751" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B751" s="13"/>
     </row>
-    <row r="752">
+    <row r="752" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B752" s="13"/>
     </row>
-    <row r="753">
+    <row r="753" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B753" s="13"/>
     </row>
-    <row r="754">
+    <row r="754" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B754" s="13"/>
     </row>
-    <row r="755">
+    <row r="755" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B755" s="13"/>
     </row>
-    <row r="756">
+    <row r="756" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B756" s="13"/>
     </row>
-    <row r="757">
+    <row r="757" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B757" s="13"/>
     </row>
-    <row r="758">
+    <row r="758" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B758" s="13"/>
     </row>
-    <row r="759">
+    <row r="759" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B759" s="13"/>
     </row>
-    <row r="760">
+    <row r="760" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B760" s="13"/>
     </row>
-    <row r="761">
+    <row r="761" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B761" s="13"/>
     </row>
-    <row r="762">
+    <row r="762" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B762" s="13"/>
     </row>
-    <row r="763">
+    <row r="763" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B763" s="13"/>
     </row>
-    <row r="764">
+    <row r="764" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B764" s="13"/>
     </row>
-    <row r="765">
+    <row r="765" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B765" s="13"/>
     </row>
-    <row r="766">
+    <row r="766" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B766" s="13"/>
     </row>
-    <row r="767">
+    <row r="767" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B767" s="13"/>
     </row>
-    <row r="768">
+    <row r="768" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B768" s="13"/>
     </row>
-    <row r="769">
+    <row r="769" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B769" s="13"/>
     </row>
-    <row r="770">
+    <row r="770" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B770" s="13"/>
     </row>
-    <row r="771">
+    <row r="771" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B771" s="13"/>
     </row>
-    <row r="772">
+    <row r="772" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B772" s="13"/>
     </row>
-    <row r="773">
+    <row r="773" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B773" s="13"/>
     </row>
-    <row r="774">
+    <row r="774" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B774" s="13"/>
     </row>
-    <row r="775">
+    <row r="775" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B775" s="13"/>
     </row>
-    <row r="776">
+    <row r="776" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B776" s="13"/>
     </row>
-    <row r="777">
+    <row r="777" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B777" s="13"/>
     </row>
-    <row r="778">
+    <row r="778" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B778" s="13"/>
     </row>
-    <row r="779">
+    <row r="779" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B779" s="13"/>
     </row>
-    <row r="780">
+    <row r="780" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B780" s="13"/>
     </row>
-    <row r="781">
+    <row r="781" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B781" s="13"/>
     </row>
-    <row r="782">
+    <row r="782" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B782" s="13"/>
     </row>
-    <row r="783">
+    <row r="783" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B783" s="13"/>
     </row>
-    <row r="784">
+    <row r="784" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B784" s="13"/>
     </row>
-    <row r="785">
+    <row r="785" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B785" s="13"/>
     </row>
-    <row r="786">
+    <row r="786" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B786" s="13"/>
     </row>
-    <row r="787">
+    <row r="787" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B787" s="13"/>
     </row>
-    <row r="788">
+    <row r="788" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B788" s="13"/>
     </row>
-    <row r="789">
+    <row r="789" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B789" s="13"/>
     </row>
-    <row r="790">
+    <row r="790" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B790" s="13"/>
     </row>
-    <row r="791">
+    <row r="791" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B791" s="13"/>
     </row>
-    <row r="792">
+    <row r="792" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B792" s="13"/>
     </row>
-    <row r="793">
+    <row r="793" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B793" s="13"/>
     </row>
-    <row r="794">
+    <row r="794" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B794" s="13"/>
     </row>
-    <row r="795">
+    <row r="795" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B795" s="13"/>
     </row>
-    <row r="796">
+    <row r="796" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B796" s="13"/>
     </row>
-    <row r="797">
+    <row r="797" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B797" s="13"/>
     </row>
-    <row r="798">
+    <row r="798" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B798" s="13"/>
     </row>
-    <row r="799">
+    <row r="799" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B799" s="13"/>
     </row>
-    <row r="800">
+    <row r="800" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B800" s="13"/>
     </row>
-    <row r="801">
+    <row r="801" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B801" s="13"/>
     </row>
-    <row r="802">
+    <row r="802" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B802" s="13"/>
     </row>
-    <row r="803">
+    <row r="803" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B803" s="13"/>
     </row>
-    <row r="804">
+    <row r="804" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B804" s="13"/>
     </row>
-    <row r="805">
+    <row r="805" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B805" s="13"/>
     </row>
-    <row r="806">
+    <row r="806" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B806" s="13"/>
     </row>
-    <row r="807">
+    <row r="807" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B807" s="13"/>
     </row>
-    <row r="808">
+    <row r="808" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B808" s="13"/>
     </row>
-    <row r="809">
+    <row r="809" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B809" s="13"/>
     </row>
-    <row r="810">
+    <row r="810" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B810" s="13"/>
     </row>
-    <row r="811">
+    <row r="811" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B811" s="13"/>
     </row>
-    <row r="812">
+    <row r="812" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B812" s="13"/>
     </row>
-    <row r="813">
+    <row r="813" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B813" s="13"/>
     </row>
-    <row r="814">
+    <row r="814" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B814" s="13"/>
     </row>
-    <row r="815">
+    <row r="815" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B815" s="13"/>
     </row>
-    <row r="816">
+    <row r="816" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B816" s="13"/>
     </row>
-    <row r="817">
+    <row r="817" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B817" s="13"/>
     </row>
-    <row r="818">
+    <row r="818" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B818" s="13"/>
     </row>
-    <row r="819">
+    <row r="819" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B819" s="13"/>
     </row>
-    <row r="820">
+    <row r="820" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B820" s="13"/>
     </row>
-    <row r="821">
+    <row r="821" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B821" s="13"/>
     </row>
-    <row r="822">
+    <row r="822" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B822" s="13"/>
     </row>
-    <row r="823">
+    <row r="823" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B823" s="13"/>
     </row>
-    <row r="824">
+    <row r="824" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B824" s="13"/>
     </row>
-    <row r="825">
+    <row r="825" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B825" s="13"/>
     </row>
-    <row r="826">
+    <row r="826" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B826" s="13"/>
     </row>
-    <row r="827">
+    <row r="827" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B827" s="13"/>
     </row>
-    <row r="828">
+    <row r="828" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B828" s="13"/>
     </row>
-    <row r="829">
+    <row r="829" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B829" s="13"/>
     </row>
-    <row r="830">
+    <row r="830" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B830" s="13"/>
     </row>
-    <row r="831">
+    <row r="831" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B831" s="13"/>
     </row>
-    <row r="832">
+    <row r="832" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B832" s="13"/>
     </row>
-    <row r="833">
+    <row r="833" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B833" s="13"/>
     </row>
-    <row r="834">
+    <row r="834" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B834" s="13"/>
     </row>
-    <row r="835">
+    <row r="835" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B835" s="13"/>
     </row>
-    <row r="836">
+    <row r="836" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B836" s="13"/>
     </row>
-    <row r="837">
+    <row r="837" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B837" s="13"/>
     </row>
-    <row r="838">
+    <row r="838" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B838" s="13"/>
     </row>
-    <row r="839">
+    <row r="839" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B839" s="13"/>
     </row>
-    <row r="840">
+    <row r="840" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B840" s="13"/>
     </row>
-    <row r="841">
+    <row r="841" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B841" s="13"/>
     </row>
-    <row r="842">
+    <row r="842" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B842" s="13"/>
     </row>
-    <row r="843">
+    <row r="843" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B843" s="13"/>
     </row>
-    <row r="844">
+    <row r="844" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B844" s="13"/>
     </row>
-    <row r="845">
+    <row r="845" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B845" s="13"/>
     </row>
-    <row r="846">
+    <row r="846" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B846" s="13"/>
     </row>
-    <row r="847">
+    <row r="847" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B847" s="13"/>
     </row>
-    <row r="848">
+    <row r="848" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B848" s="13"/>
     </row>
-    <row r="849">
+    <row r="849" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B849" s="13"/>
     </row>
-    <row r="850">
+    <row r="850" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B850" s="13"/>
     </row>
-    <row r="851">
+    <row r="851" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B851" s="13"/>
     </row>
-    <row r="852">
+    <row r="852" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B852" s="13"/>
     </row>
-    <row r="853">
+    <row r="853" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B853" s="13"/>
     </row>
-    <row r="854">
+    <row r="854" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B854" s="13"/>
     </row>
-    <row r="855">
+    <row r="855" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B855" s="13"/>
     </row>
-    <row r="856">
+    <row r="856" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B856" s="13"/>
     </row>
-    <row r="857">
+    <row r="857" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B857" s="13"/>
     </row>
-    <row r="858">
+    <row r="858" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B858" s="13"/>
     </row>
-    <row r="859">
+    <row r="859" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B859" s="13"/>
     </row>
-    <row r="860">
+    <row r="860" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B860" s="13"/>
     </row>
-    <row r="861">
+    <row r="861" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B861" s="13"/>
     </row>
-    <row r="862">
+    <row r="862" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B862" s="13"/>
     </row>
-    <row r="863">
+    <row r="863" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B863" s="13"/>
     </row>
-    <row r="864">
+    <row r="864" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B864" s="13"/>
     </row>
-    <row r="865">
+    <row r="865" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B865" s="13"/>
     </row>
-    <row r="866">
+    <row r="866" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B866" s="13"/>
     </row>
-    <row r="867">
+    <row r="867" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B867" s="13"/>
     </row>
-    <row r="868">
+    <row r="868" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B868" s="13"/>
     </row>
-    <row r="869">
+    <row r="869" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B869" s="13"/>
     </row>
-    <row r="870">
+    <row r="870" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B870" s="13"/>
     </row>
-    <row r="871">
+    <row r="871" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B871" s="13"/>
     </row>
-    <row r="872">
+    <row r="872" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B872" s="13"/>
     </row>
-    <row r="873">
+    <row r="873" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B873" s="13"/>
     </row>
-    <row r="874">
+    <row r="874" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B874" s="13"/>
     </row>
-    <row r="875">
+    <row r="875" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B875" s="13"/>
     </row>
-    <row r="876">
+    <row r="876" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B876" s="13"/>
     </row>
-    <row r="877">
+    <row r="877" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B877" s="13"/>
     </row>
-    <row r="878">
+    <row r="878" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B878" s="13"/>
     </row>
-    <row r="879">
+    <row r="879" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B879" s="13"/>
     </row>
-    <row r="880">
+    <row r="880" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B880" s="13"/>
     </row>
-    <row r="881">
+    <row r="881" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B881" s="13"/>
     </row>
-    <row r="882">
+    <row r="882" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B882" s="13"/>
     </row>
-    <row r="883">
+    <row r="883" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B883" s="13"/>
     </row>
-    <row r="884">
+    <row r="884" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B884" s="13"/>
     </row>
-    <row r="885">
+    <row r="885" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B885" s="13"/>
     </row>
-    <row r="886">
+    <row r="886" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B886" s="13"/>
     </row>
-    <row r="887">
+    <row r="887" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B887" s="13"/>
     </row>
-    <row r="888">
+    <row r="888" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B888" s="13"/>
     </row>
-    <row r="889">
+    <row r="889" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B889" s="13"/>
     </row>
-    <row r="890">
+    <row r="890" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B890" s="13"/>
     </row>
-    <row r="891">
+    <row r="891" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B891" s="13"/>
     </row>
-    <row r="892">
+    <row r="892" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B892" s="13"/>
     </row>
-    <row r="893">
+    <row r="893" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B893" s="13"/>
     </row>
-    <row r="894">
+    <row r="894" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B894" s="13"/>
     </row>
-    <row r="895">
+    <row r="895" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B895" s="13"/>
     </row>
-    <row r="896">
+    <row r="896" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B896" s="13"/>
     </row>
-    <row r="897">
+    <row r="897" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B897" s="13"/>
     </row>
-    <row r="898">
+    <row r="898" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B898" s="13"/>
     </row>
-    <row r="899">
+    <row r="899" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B899" s="13"/>
     </row>
-    <row r="900">
+    <row r="900" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B900" s="13"/>
     </row>
-    <row r="901">
+    <row r="901" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B901" s="13"/>
     </row>
-    <row r="902">
+    <row r="902" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B902" s="13"/>
     </row>
-    <row r="903">
+    <row r="903" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B903" s="13"/>
     </row>
-    <row r="904">
+    <row r="904" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B904" s="13"/>
     </row>
-    <row r="905">
+    <row r="905" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B905" s="13"/>
     </row>
-    <row r="906">
+    <row r="906" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B906" s="13"/>
     </row>
-    <row r="907">
+    <row r="907" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B907" s="13"/>
     </row>
-    <row r="908">
+    <row r="908" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B908" s="13"/>
     </row>
-    <row r="909">
+    <row r="909" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B909" s="13"/>
     </row>
-    <row r="910">
+    <row r="910" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B910" s="13"/>
     </row>
-    <row r="911">
+    <row r="911" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B911" s="13"/>
     </row>
-    <row r="912">
+    <row r="912" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B912" s="13"/>
     </row>
-    <row r="913">
+    <row r="913" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B913" s="13"/>
     </row>
-    <row r="914">
+    <row r="914" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B914" s="13"/>
     </row>
-    <row r="915">
+    <row r="915" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B915" s="13"/>
     </row>
-    <row r="916">
+    <row r="916" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B916" s="13"/>
     </row>
-    <row r="917">
+    <row r="917" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B917" s="13"/>
     </row>
-    <row r="918">
+    <row r="918" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B918" s="13"/>
     </row>
-    <row r="919">
+    <row r="919" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B919" s="13"/>
     </row>
-    <row r="920">
+    <row r="920" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B920" s="13"/>
     </row>
-    <row r="921">
+    <row r="921" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B921" s="13"/>
     </row>
-    <row r="922">
+    <row r="922" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B922" s="13"/>
     </row>
-    <row r="923">
+    <row r="923" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B923" s="13"/>
     </row>
-    <row r="924">
+    <row r="924" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B924" s="13"/>
     </row>
-    <row r="925">
+    <row r="925" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B925" s="13"/>
     </row>
-    <row r="926">
+    <row r="926" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B926" s="13"/>
     </row>
-    <row r="927">
+    <row r="927" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B927" s="13"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B928" s="13"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B929" s="13"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B930" s="13"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B931" s="13"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B932" s="13"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B933" s="13"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B934" s="13"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B935" s="13"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B936" s="13"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B937" s="13"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B938" s="13"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B939" s="13"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B940" s="13"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B941" s="13"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B942" s="13"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B943" s="13"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B944" s="13"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B945" s="13"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B946" s="13"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B947" s="13"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B948" s="13"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B949" s="13"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B950" s="13"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B951" s="13"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B952" s="13"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B953" s="13"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B954" s="13"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B955" s="13"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B956" s="13"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B957" s="13"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B958" s="13"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B959" s="13"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B960" s="13"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
